--- a/AAII_Financials/Quarterly/MLGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MLGO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -727,19 +727,19 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>36400</v>
+        <v>36600</v>
       </c>
       <c r="E8" s="3">
         <v>2500</v>
       </c>
       <c r="F8" s="3">
-        <v>12000</v>
+        <v>12100</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H8" s="3">
-        <v>47700</v>
+        <v>48100</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>4</v>
@@ -765,19 +765,19 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>25300</v>
+        <v>25500</v>
       </c>
       <c r="E9" s="3">
         <v>1800</v>
       </c>
       <c r="F9" s="3">
-        <v>9400</v>
+        <v>9500</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H9" s="3">
-        <v>38200</v>
+        <v>38400</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>4</v>
@@ -803,7 +803,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>11100</v>
+        <v>11200</v>
       </c>
       <c r="E10" s="3">
         <v>700</v>
@@ -857,7 +857,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>12700</v>
+        <v>12800</v>
       </c>
       <c r="E12" s="3">
         <v>700</v>
@@ -1022,19 +1022,19 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>42400</v>
+        <v>42700</v>
       </c>
       <c r="E17" s="3">
         <v>2700</v>
       </c>
       <c r="F17" s="3">
-        <v>13000</v>
+        <v>13100</v>
       </c>
       <c r="G17" s="3">
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>45900</v>
+        <v>46200</v>
       </c>
       <c r="I17" s="3">
         <v>0</v>
@@ -1060,7 +1060,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-6000</v>
+        <v>-6100</v>
       </c>
       <c r="E18" s="3">
         <v>-200</v>
@@ -1072,7 +1072,7 @@
         <v>4</v>
       </c>
       <c r="H18" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>4</v>
@@ -1380,7 +1380,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-5100</v>
+        <v>-5200</v>
       </c>
       <c r="E27" s="3">
         <v>-200</v>
@@ -1608,7 +1608,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-5100</v>
+        <v>-5200</v>
       </c>
       <c r="E33" s="3">
         <v>-200</v>
@@ -1684,7 +1684,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-5100</v>
+        <v>-5200</v>
       </c>
       <c r="E35" s="3">
         <v>-200</v>
@@ -1797,13 +1797,13 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>19100</v>
+        <v>19300</v>
       </c>
       <c r="E41" s="3">
         <v>2900</v>
       </c>
       <c r="F41" s="3">
-        <v>41100</v>
+        <v>41400</v>
       </c>
       <c r="G41" s="3">
         <v>0</v>
@@ -1873,7 +1873,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>30200</v>
+        <v>30400</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
@@ -1949,7 +1949,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="E45" s="3">
         <v>5000</v>
@@ -1987,13 +1987,13 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>55700</v>
+        <v>56100</v>
       </c>
       <c r="E46" s="3">
-        <v>8100</v>
+        <v>8200</v>
       </c>
       <c r="F46" s="3">
-        <v>53100</v>
+        <v>53500</v>
       </c>
       <c r="G46" s="3">
         <v>0</v>
@@ -2034,16 +2034,16 @@
         <v>200</v>
       </c>
       <c r="G47" s="3">
+        <v>6700</v>
+      </c>
+      <c r="H47" s="3">
         <v>6600</v>
-      </c>
-      <c r="H47" s="3">
-        <v>6500</v>
       </c>
       <c r="I47" s="3">
         <v>6500</v>
       </c>
       <c r="J47" s="3">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="K47" s="3">
         <v>46500</v>
@@ -2101,13 +2101,13 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>15600</v>
+        <v>15700</v>
       </c>
       <c r="E49" s="3">
         <v>2300</v>
       </c>
       <c r="F49" s="3">
-        <v>15600</v>
+        <v>15700</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>4</v>
@@ -2291,25 +2291,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>71700</v>
+        <v>72100</v>
       </c>
       <c r="E54" s="3">
-        <v>10400</v>
+        <v>10500</v>
       </c>
       <c r="F54" s="3">
-        <v>69300</v>
+        <v>69800</v>
       </c>
       <c r="G54" s="3">
         <v>6700</v>
       </c>
       <c r="H54" s="3">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="I54" s="3">
         <v>6500</v>
       </c>
       <c r="J54" s="3">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="K54" s="3">
         <v>46500</v>
@@ -2475,13 +2475,13 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>11600</v>
+        <v>11700</v>
       </c>
       <c r="E60" s="3">
         <v>1200</v>
       </c>
       <c r="F60" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="G60" s="3">
         <v>300</v>
@@ -2703,13 +2703,13 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>11400</v>
+        <v>11500</v>
       </c>
       <c r="E66" s="3">
         <v>1200</v>
       </c>
       <c r="F66" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="G66" s="3">
         <v>500</v>
@@ -2909,13 +2909,13 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>15000</v>
+        <v>15100</v>
       </c>
       <c r="E72" s="3">
         <v>2700</v>
       </c>
       <c r="F72" s="3">
-        <v>19500</v>
+        <v>19700</v>
       </c>
       <c r="G72" s="3">
         <v>-500</v>
@@ -3061,25 +3061,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>60300</v>
+        <v>60700</v>
       </c>
       <c r="E76" s="3">
-        <v>9200</v>
+        <v>9300</v>
       </c>
       <c r="F76" s="3">
-        <v>64200</v>
+        <v>64600</v>
       </c>
       <c r="G76" s="3">
         <v>6200</v>
       </c>
       <c r="H76" s="3">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="I76" s="3">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="J76" s="3">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="K76" s="3">
         <v>44700</v>
@@ -3180,7 +3180,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-5100</v>
+        <v>-5200</v>
       </c>
       <c r="E81" s="3">
         <v>-200</v>
@@ -3836,7 +3836,7 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-17100</v>
+        <v>-17200</v>
       </c>
       <c r="E100" s="3">
         <v>-2700</v>
@@ -3912,7 +3912,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-22000</v>
+        <v>-22100</v>
       </c>
       <c r="E102" s="3">
         <v>-2900</v>

--- a/AAII_Financials/Quarterly/MLGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MLGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
   <si>
     <t>MLGO</t>
   </si>
@@ -656,102 +656,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>36600</v>
+        <v>80100</v>
       </c>
       <c r="E8" s="3">
+        <v>36400</v>
+      </c>
+      <c r="F8" s="3">
         <v>2500</v>
       </c>
-      <c r="F8" s="3">
-        <v>12100</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3">
-        <v>48100</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
+      <c r="G8" s="3">
+        <v>81000</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3">
+        <v>47800</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -759,28 +763,31 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>25500</v>
+        <v>56100</v>
       </c>
       <c r="E9" s="3">
+        <v>25300</v>
+      </c>
+      <c r="F9" s="3">
         <v>1800</v>
       </c>
-      <c r="F9" s="3">
-        <v>9500</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="3">
-        <v>38400</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
+      <c r="G9" s="3">
+        <v>63400</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" s="3">
+        <v>38200</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>4</v>
@@ -797,29 +804,32 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>11200</v>
+        <v>24000</v>
       </c>
       <c r="E10" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F10" s="3">
         <v>700</v>
       </c>
-      <c r="F10" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="G10" s="3">
+        <v>17600</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="3">
         <v>9600</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>4</v>
       </c>
@@ -835,8 +845,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,29 +864,30 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>12800</v>
+        <v>22300</v>
       </c>
       <c r="E12" s="3">
+        <v>12700</v>
+      </c>
+      <c r="F12" s="3">
         <v>700</v>
       </c>
-      <c r="F12" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="G12" s="3">
+        <v>12900</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="3">
         <v>5600</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>4</v>
       </c>
@@ -889,8 +903,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,37 +944,40 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E14" s="3">
         <v>3200</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -965,8 +985,11 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,8 +1026,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,84 +1042,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>42700</v>
+        <v>114000</v>
       </c>
       <c r="E17" s="3">
+        <v>42400</v>
+      </c>
+      <c r="F17" s="3">
         <v>2700</v>
       </c>
-      <c r="F17" s="3">
-        <v>13100</v>
-      </c>
       <c r="G17" s="3">
-        <v>0</v>
+        <v>88300</v>
       </c>
       <c r="H17" s="3">
-        <v>46200</v>
+        <v>0</v>
       </c>
       <c r="I17" s="3">
-        <v>0</v>
+        <v>45800</v>
       </c>
       <c r="J17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
         <v>300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>200</v>
-      </c>
-      <c r="M17" s="3">
-        <v>100</v>
       </c>
       <c r="N17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-6100</v>
+        <v>-33900</v>
       </c>
       <c r="E18" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-200</v>
       </c>
-      <c r="F18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
+      <c r="G18" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-100</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3">
         <v>-200</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-100</v>
       </c>
       <c r="N18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,37 +1141,38 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>300</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1146,25 +1180,28 @@
       <c r="N20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-200</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3">
-        <v>2700</v>
+      <c r="G21" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>4</v>
@@ -1184,8 +1221,11 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1222,75 +1262,81 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-37100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-200</v>
       </c>
-      <c r="F23" s="3">
-        <v>-1100</v>
-      </c>
       <c r="G23" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="H23" s="3">
         <v>100</v>
       </c>
-      <c r="H23" s="3">
-        <v>2000</v>
-      </c>
       <c r="I23" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="J23" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
         <v>-300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-200</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-100</v>
       </c>
       <c r="N23" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1298,8 +1344,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,84 +1385,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-36800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-200</v>
       </c>
-      <c r="F26" s="3">
-        <v>-1000</v>
-      </c>
       <c r="G26" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="H26" s="3">
         <v>100</v>
       </c>
-      <c r="H26" s="3">
-        <v>2100</v>
-      </c>
       <c r="I26" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="J26" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
         <v>-300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-200</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-100</v>
       </c>
       <c r="N26" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-5200</v>
+        <v>-37100</v>
       </c>
       <c r="E27" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-200</v>
       </c>
-      <c r="F27" s="3">
-        <v>-1000</v>
-      </c>
       <c r="G27" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="H27" s="3">
         <v>100</v>
       </c>
-      <c r="H27" s="3">
-        <v>2100</v>
-      </c>
       <c r="I27" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="J27" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
         <v>-300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-200</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-100</v>
       </c>
       <c r="N27" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1508,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1549,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1590,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,37 +1631,40 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
-        <v>100</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -1602,46 +1672,52 @@
       <c r="N32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-5200</v>
+        <v>-37100</v>
       </c>
       <c r="E33" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-200</v>
       </c>
-      <c r="F33" s="3">
-        <v>-1000</v>
-      </c>
       <c r="G33" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="H33" s="3">
         <v>100</v>
       </c>
-      <c r="H33" s="3">
-        <v>2100</v>
-      </c>
       <c r="I33" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
         <v>-300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-200</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-100</v>
       </c>
       <c r="N33" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,89 +1754,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-5200</v>
+        <v>-37100</v>
       </c>
       <c r="E35" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-200</v>
       </c>
-      <c r="F35" s="3">
-        <v>-1000</v>
-      </c>
       <c r="G35" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="H35" s="3">
         <v>100</v>
       </c>
-      <c r="H35" s="3">
-        <v>2100</v>
-      </c>
       <c r="I35" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>-300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-200</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-100</v>
       </c>
       <c r="N35" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1860,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,22 +1877,23 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>19300</v>
+        <v>43800</v>
       </c>
       <c r="E41" s="3">
+        <v>19200</v>
+      </c>
+      <c r="F41" s="3">
         <v>2900</v>
       </c>
-      <c r="F41" s="3">
-        <v>41400</v>
-      </c>
       <c r="G41" s="3">
-        <v>0</v>
+        <v>41100</v>
       </c>
       <c r="H41" s="3">
         <v>0</v>
@@ -1824,36 +1911,39 @@
         <v>0</v>
       </c>
       <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
         <v>200</v>
       </c>
-      <c r="N41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
+        <v>2500</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -1867,23 +1957,26 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>30400</v>
+        <v>3300</v>
       </c>
       <c r="E43" s="3">
+        <v>30200</v>
+      </c>
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8300</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>4</v>
       </c>
@@ -1896,8 +1989,8 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -1905,23 +1998,26 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
         <v>0</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3">
         <v>100</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>4</v>
       </c>
@@ -1934,8 +2030,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -1943,23 +2039,26 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="E45" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F45" s="3">
         <v>5000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4400</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
       <c r="H45" s="3">
         <v>0</v>
       </c>
@@ -1973,30 +2072,33 @@
         <v>0</v>
       </c>
       <c r="L45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3">
+        <v>100</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>56100</v>
+        <v>56400</v>
       </c>
       <c r="E46" s="3">
-        <v>8200</v>
+        <v>55800</v>
       </c>
       <c r="F46" s="3">
-        <v>53500</v>
+        <v>8100</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>53100</v>
       </c>
       <c r="H46" s="3">
         <v>0</v>
@@ -2011,33 +2113,36 @@
         <v>0</v>
       </c>
       <c r="L46" s="3">
+        <v>0</v>
+      </c>
+      <c r="M46" s="3">
         <v>100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>300</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
         <v>200</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
       <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
         <v>200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6700</v>
-      </c>
-      <c r="H47" s="3">
-        <v>6600</v>
       </c>
       <c r="I47" s="3">
         <v>6500</v>
@@ -2046,7 +2151,7 @@
         <v>6500</v>
       </c>
       <c r="K47" s="3">
-        <v>46500</v>
+        <v>6500</v>
       </c>
       <c r="L47" s="3">
         <v>46500</v>
@@ -2054,11 +2159,14 @@
       <c r="M47" s="3">
         <v>46500</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>46500</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2066,14 +2174,14 @@
         <v>200</v>
       </c>
       <c r="E48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
         <v>300</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2086,8 +2194,8 @@
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -2095,22 +2203,25 @@
       <c r="N48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>15700</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>15600</v>
+      </c>
+      <c r="F49" s="3">
         <v>2300</v>
       </c>
-      <c r="F49" s="3">
-        <v>15700</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>4</v>
+      <c r="G49" s="3">
+        <v>15600</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>4</v>
@@ -2124,8 +2235,8 @@
       <c r="K49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2133,8 +2244,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2285,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,23 +2326,26 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
       </c>
       <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
       <c r="H52" s="3">
         <v>0</v>
       </c>
@@ -2245,10 +2365,13 @@
         <v>0</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,25 +2408,28 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>72100</v>
+        <v>56700</v>
       </c>
       <c r="E54" s="3">
-        <v>10500</v>
+        <v>71700</v>
       </c>
       <c r="F54" s="3">
-        <v>69800</v>
+        <v>10400</v>
       </c>
       <c r="G54" s="3">
+        <v>69400</v>
+      </c>
+      <c r="H54" s="3">
         <v>6700</v>
-      </c>
-      <c r="H54" s="3">
-        <v>6600</v>
       </c>
       <c r="I54" s="3">
         <v>6500</v>
@@ -2312,19 +2438,22 @@
         <v>6500</v>
       </c>
       <c r="K54" s="3">
+        <v>6500</v>
+      </c>
+      <c r="L54" s="3">
         <v>46500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>46600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>46800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2468,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,23 +2485,24 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E57" s="3">
         <v>4900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2384,8 +2515,8 @@
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -2393,61 +2524,67 @@
       <c r="N57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E58" s="3">
         <v>1200</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>200</v>
-      </c>
-      <c r="I58" s="3">
-        <v>100</v>
       </c>
       <c r="J58" s="3">
         <v>100</v>
       </c>
       <c r="K58" s="3">
+        <v>100</v>
+      </c>
+      <c r="L58" s="3">
         <v>200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2700</v>
       </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
       <c r="H59" s="3">
         <v>0</v>
       </c>
@@ -2458,57 +2595,63 @@
         <v>0</v>
       </c>
       <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
       <c r="M59" s="3">
         <v>0</v>
       </c>
       <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>11700</v>
+        <v>11800</v>
       </c>
       <c r="E60" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F60" s="3">
         <v>1200</v>
       </c>
-      <c r="F60" s="3">
-        <v>4700</v>
-      </c>
       <c r="G60" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H60" s="3">
         <v>300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>200</v>
-      </c>
-      <c r="I60" s="3">
-        <v>100</v>
       </c>
       <c r="J60" s="3">
         <v>100</v>
       </c>
       <c r="K60" s="3">
+        <v>100</v>
+      </c>
+      <c r="L60" s="3">
         <v>300</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
       <c r="N60" s="3">
+        <v>0</v>
+      </c>
+      <c r="O60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2545,22 +2688,25 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
         <v>300</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
       <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
         <v>300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>200</v>
       </c>
       <c r="H62" s="3">
         <v>200</v>
@@ -2572,7 +2718,7 @@
         <v>200</v>
       </c>
       <c r="K62" s="3">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="L62" s="3">
         <v>1500</v>
@@ -2580,11 +2726,14 @@
       <c r="M62" s="3">
         <v>1500</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2770,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2811,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,46 +2852,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>11500</v>
+        <v>12300</v>
       </c>
       <c r="E66" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F66" s="3">
         <v>1200</v>
       </c>
-      <c r="F66" s="3">
-        <v>5200</v>
-      </c>
       <c r="G66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="H66" s="3">
         <v>500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>400</v>
-      </c>
-      <c r="I66" s="3">
-        <v>300</v>
       </c>
       <c r="J66" s="3">
         <v>300</v>
       </c>
       <c r="K66" s="3">
+        <v>300</v>
+      </c>
+      <c r="L66" s="3">
         <v>1800</v>
-      </c>
-      <c r="L66" s="3">
-        <v>1600</v>
       </c>
       <c r="M66" s="3">
         <v>1600</v>
       </c>
       <c r="N66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O66" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +2912,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +2951,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +2992,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3033,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,46 +3074,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>15100</v>
+        <v>-8800</v>
       </c>
       <c r="E72" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F72" s="3">
         <v>2700</v>
       </c>
-      <c r="F72" s="3">
-        <v>19700</v>
-      </c>
       <c r="G72" s="3">
+        <v>19600</v>
+      </c>
+      <c r="H72" s="3">
         <v>-500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-400</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-300</v>
       </c>
       <c r="J72" s="3">
         <v>-300</v>
       </c>
       <c r="K72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L72" s="3">
         <v>-1800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3156,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3197,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3238,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>60700</v>
+        <v>44400</v>
       </c>
       <c r="E76" s="3">
-        <v>9300</v>
+        <v>60300</v>
       </c>
       <c r="F76" s="3">
-        <v>64600</v>
+        <v>9200</v>
       </c>
       <c r="G76" s="3">
-        <v>6200</v>
+        <v>64200</v>
       </c>
       <c r="H76" s="3">
         <v>6200</v>
       </c>
       <c r="I76" s="3">
+        <v>6100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K76" s="3">
         <v>6200</v>
       </c>
-      <c r="J76" s="3">
-        <v>6200</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>44700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>45000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>45200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,89 +3320,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-5200</v>
+        <v>-37100</v>
       </c>
       <c r="E81" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-200</v>
       </c>
-      <c r="F81" s="3">
-        <v>-1000</v>
-      </c>
       <c r="G81" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="H81" s="3">
         <v>100</v>
       </c>
-      <c r="H81" s="3">
-        <v>2100</v>
-      </c>
       <c r="I81" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
         <v>-300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-200</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-100</v>
       </c>
       <c r="N81" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,25 +3426,26 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" s="3">
-        <v>600</v>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>4</v>
@@ -3257,8 +3456,8 @@
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -3266,8 +3465,11 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3506,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3547,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3588,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3629,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,8 +3670,11 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3465,37 +3682,40 @@
         <v>-6300</v>
       </c>
       <c r="E89" s="3">
-        <v>0</v>
+        <v>-6300</v>
       </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I89" s="3">
         <v>300</v>
       </c>
-      <c r="G89" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H89" s="3">
-        <v>300</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
         <v>0</v>
       </c>
       <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>-300</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-200</v>
       </c>
       <c r="M89" s="3">
         <v>-200</v>
       </c>
       <c r="N89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+        <v>-200</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,8 +3730,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3525,7 +3746,7 @@
         <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -3548,8 +3769,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +3810,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,29 +3851,32 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E94" s="3">
         <v>200</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H94" s="3">
         <v>-2700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>2500</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
@@ -3657,13 +3887,16 @@
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-46500</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,8 +3911,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3716,8 +3950,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +3991,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4032,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,63 +4073,69 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-17200</v>
+        <v>10600</v>
       </c>
       <c r="E100" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2700</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-600</v>
       </c>
       <c r="G100" s="3">
         <v>-300</v>
       </c>
       <c r="H100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>46900</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>700</v>
+      </c>
+      <c r="E101" s="3">
         <v>1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H101" s="3">
-        <v>800</v>
+      <c r="G101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>4</v>
@@ -3897,8 +4146,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -3906,29 +4155,32 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-22100</v>
+        <v>2700</v>
       </c>
       <c r="E102" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2900</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H102" s="3">
         <v>-4200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4200</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
@@ -3936,12 +4188,15 @@
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MLGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MLGO_QTR_FIN.xlsx
@@ -731,22 +731,22 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>80100</v>
+        <v>81800</v>
       </c>
       <c r="E8" s="3">
-        <v>36400</v>
+        <v>37200</v>
       </c>
       <c r="F8" s="3">
         <v>2500</v>
       </c>
       <c r="G8" s="3">
-        <v>81000</v>
+        <v>82600</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I8" s="3">
-        <v>47800</v>
+        <v>48800</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -772,22 +772,22 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>56100</v>
+        <v>57200</v>
       </c>
       <c r="E9" s="3">
-        <v>25300</v>
+        <v>25800</v>
       </c>
       <c r="F9" s="3">
         <v>1800</v>
       </c>
       <c r="G9" s="3">
-        <v>63400</v>
+        <v>64700</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I9" s="3">
-        <v>38200</v>
+        <v>39000</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>4</v>
@@ -813,22 +813,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="E10" s="3">
-        <v>11100</v>
+        <v>11300</v>
       </c>
       <c r="F10" s="3">
         <v>700</v>
       </c>
       <c r="G10" s="3">
-        <v>17600</v>
+        <v>18000</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I10" s="3">
-        <v>9600</v>
+        <v>9800</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>4</v>
@@ -871,22 +871,22 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>22300</v>
+        <v>22700</v>
       </c>
       <c r="E12" s="3">
-        <v>12700</v>
+        <v>13000</v>
       </c>
       <c r="F12" s="3">
         <v>700</v>
       </c>
       <c r="G12" s="3">
-        <v>12900</v>
+        <v>13200</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I12" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>4</v>
@@ -953,7 +953,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>15600</v>
+        <v>15900</v>
       </c>
       <c r="E14" s="3">
         <v>3200</v>
@@ -962,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>7000</v>
+        <v>7200</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I14" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1049,25 +1049,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>114000</v>
+        <v>116300</v>
       </c>
       <c r="E17" s="3">
-        <v>42400</v>
+        <v>43300</v>
       </c>
       <c r="F17" s="3">
         <v>2700</v>
       </c>
       <c r="G17" s="3">
-        <v>88300</v>
+        <v>90100</v>
       </c>
       <c r="H17" s="3">
         <v>0</v>
       </c>
       <c r="I17" s="3">
-        <v>45800</v>
+        <v>46700</v>
       </c>
       <c r="J17" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -1090,16 +1090,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-33900</v>
+        <v>-34600</v>
       </c>
       <c r="E18" s="3">
-        <v>-6000</v>
+        <v>-6200</v>
       </c>
       <c r="F18" s="3">
         <v>-200</v>
       </c>
       <c r="G18" s="3">
-        <v>-7300</v>
+        <v>-7400</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>4</v>
@@ -1108,7 +1108,7 @@
         <v>2000</v>
       </c>
       <c r="J18" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>4</v>
@@ -1148,7 +1148,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-3200</v>
+        <v>-3300</v>
       </c>
       <c r="E20" s="3">
         <v>200</v>
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>4</v>
@@ -1189,16 +1189,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-37000</v>
+        <v>-37700</v>
       </c>
       <c r="E21" s="3">
-        <v>-5800</v>
+        <v>-5900</v>
       </c>
       <c r="F21" s="3">
         <v>-200</v>
       </c>
       <c r="G21" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>4</v>
@@ -1271,16 +1271,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-37100</v>
+        <v>-37900</v>
       </c>
       <c r="E23" s="3">
-        <v>-5800</v>
+        <v>-5900</v>
       </c>
       <c r="F23" s="3">
         <v>-200</v>
       </c>
       <c r="G23" s="3">
-        <v>-7000</v>
+        <v>-7100</v>
       </c>
       <c r="H23" s="3">
         <v>100</v>
@@ -1312,7 +1312,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1394,16 +1394,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-36800</v>
+        <v>-37500</v>
       </c>
       <c r="E26" s="3">
-        <v>-5800</v>
+        <v>-5900</v>
       </c>
       <c r="F26" s="3">
         <v>-200</v>
       </c>
       <c r="G26" s="3">
-        <v>-6400</v>
+        <v>-6600</v>
       </c>
       <c r="H26" s="3">
         <v>100</v>
@@ -1435,22 +1435,22 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-37100</v>
+        <v>-37800</v>
       </c>
       <c r="E27" s="3">
-        <v>-5100</v>
+        <v>-5200</v>
       </c>
       <c r="F27" s="3">
         <v>-200</v>
       </c>
       <c r="G27" s="3">
-        <v>-6500</v>
+        <v>-6600</v>
       </c>
       <c r="H27" s="3">
         <v>100</v>
       </c>
       <c r="I27" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="J27" s="3">
         <v>-200</v>
@@ -1640,7 +1640,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="E32" s="3">
         <v>-200</v>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>4</v>
@@ -1681,22 +1681,22 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-37100</v>
+        <v>-37800</v>
       </c>
       <c r="E33" s="3">
-        <v>-5100</v>
+        <v>-5200</v>
       </c>
       <c r="F33" s="3">
         <v>-200</v>
       </c>
       <c r="G33" s="3">
-        <v>-6500</v>
+        <v>-6600</v>
       </c>
       <c r="H33" s="3">
         <v>100</v>
       </c>
       <c r="I33" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="J33" s="3">
         <v>-200</v>
@@ -1763,22 +1763,22 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-37100</v>
+        <v>-37800</v>
       </c>
       <c r="E35" s="3">
-        <v>-5100</v>
+        <v>-5200</v>
       </c>
       <c r="F35" s="3">
         <v>-200</v>
       </c>
       <c r="G35" s="3">
-        <v>-6500</v>
+        <v>-6600</v>
       </c>
       <c r="H35" s="3">
         <v>100</v>
       </c>
       <c r="I35" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="J35" s="3">
         <v>-200</v>
@@ -1884,16 +1884,16 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>43800</v>
+        <v>44700</v>
       </c>
       <c r="E41" s="3">
-        <v>19200</v>
+        <v>19600</v>
       </c>
       <c r="F41" s="3">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="G41" s="3">
-        <v>41100</v>
+        <v>42000</v>
       </c>
       <c r="H41" s="3">
         <v>0</v>
@@ -1925,7 +1925,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>4</v>
@@ -1966,16 +1966,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="E43" s="3">
-        <v>30200</v>
+        <v>30800</v>
       </c>
       <c r="F43" s="3">
         <v>200</v>
       </c>
       <c r="G43" s="3">
-        <v>8300</v>
+        <v>8500</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>4</v>
@@ -2048,16 +2048,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6700</v>
+        <v>6800</v>
       </c>
       <c r="E45" s="3">
-        <v>6400</v>
+        <v>6600</v>
       </c>
       <c r="F45" s="3">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="G45" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="H45" s="3">
         <v>0</v>
@@ -2089,16 +2089,16 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>56400</v>
+        <v>57600</v>
       </c>
       <c r="E46" s="3">
-        <v>55800</v>
+        <v>56900</v>
       </c>
       <c r="F46" s="3">
-        <v>8100</v>
+        <v>8300</v>
       </c>
       <c r="G46" s="3">
-        <v>53100</v>
+        <v>54200</v>
       </c>
       <c r="H46" s="3">
         <v>0</v>
@@ -2142,13 +2142,13 @@
         <v>200</v>
       </c>
       <c r="H47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="I47" s="3">
         <v>6700</v>
       </c>
-      <c r="I47" s="3">
-        <v>6500</v>
-      </c>
       <c r="J47" s="3">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="K47" s="3">
         <v>6500</v>
@@ -2215,13 +2215,13 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>15600</v>
+        <v>15900</v>
       </c>
       <c r="F49" s="3">
         <v>2300</v>
       </c>
       <c r="G49" s="3">
-        <v>15600</v>
+        <v>15900</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>4</v>
@@ -2417,25 +2417,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>56700</v>
+        <v>57900</v>
       </c>
       <c r="E54" s="3">
-        <v>71700</v>
+        <v>73200</v>
       </c>
       <c r="F54" s="3">
-        <v>10400</v>
+        <v>10700</v>
       </c>
       <c r="G54" s="3">
-        <v>69400</v>
+        <v>70800</v>
       </c>
       <c r="H54" s="3">
+        <v>6800</v>
+      </c>
+      <c r="I54" s="3">
         <v>6700</v>
       </c>
-      <c r="I54" s="3">
-        <v>6500</v>
-      </c>
       <c r="J54" s="3">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="K54" s="3">
         <v>6500</v>
@@ -2492,10 +2492,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="E57" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="F57" s="3">
         <v>300</v>
@@ -2574,10 +2574,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7000</v>
+        <v>7200</v>
       </c>
       <c r="E59" s="3">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="F59" s="3">
         <v>800</v>
@@ -2615,16 +2615,16 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11800</v>
-      </c>
-      <c r="E60" s="3">
-        <v>11600</v>
       </c>
       <c r="F60" s="3">
         <v>1200</v>
       </c>
       <c r="G60" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="H60" s="3">
         <v>300</v>
@@ -2861,16 +2861,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>12300</v>
+        <v>12600</v>
       </c>
       <c r="E66" s="3">
-        <v>11400</v>
+        <v>11600</v>
       </c>
       <c r="F66" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="G66" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="H66" s="3">
         <v>500</v>
@@ -2879,7 +2879,7 @@
         <v>400</v>
       </c>
       <c r="J66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K66" s="3">
         <v>300</v>
@@ -3083,16 +3083,16 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-8800</v>
+        <v>-9000</v>
       </c>
       <c r="E72" s="3">
-        <v>15000</v>
+        <v>15300</v>
       </c>
       <c r="F72" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="G72" s="3">
-        <v>19600</v>
+        <v>20000</v>
       </c>
       <c r="H72" s="3">
         <v>-500</v>
@@ -3247,25 +3247,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>44400</v>
+        <v>45300</v>
       </c>
       <c r="E76" s="3">
-        <v>60300</v>
+        <v>61500</v>
       </c>
       <c r="F76" s="3">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="G76" s="3">
-        <v>64200</v>
+        <v>65500</v>
       </c>
       <c r="H76" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I76" s="3">
         <v>6200</v>
       </c>
-      <c r="I76" s="3">
-        <v>6100</v>
-      </c>
       <c r="J76" s="3">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="K76" s="3">
         <v>6200</v>
@@ -3375,22 +3375,22 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-37100</v>
+        <v>-37800</v>
       </c>
       <c r="E81" s="3">
-        <v>-5100</v>
+        <v>-5200</v>
       </c>
       <c r="F81" s="3">
         <v>-200</v>
       </c>
       <c r="G81" s="3">
-        <v>-6500</v>
+        <v>-6600</v>
       </c>
       <c r="H81" s="3">
         <v>100</v>
       </c>
       <c r="I81" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="J81" s="3">
         <v>-200</v>
@@ -3679,16 +3679,16 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-6300</v>
+        <v>-6400</v>
       </c>
       <c r="E89" s="3">
-        <v>-6300</v>
+        <v>-6400</v>
       </c>
       <c r="F89" s="3">
         <v>0</v>
       </c>
       <c r="G89" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="H89" s="3">
         <v>-400</v>
@@ -3860,7 +3860,7 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2300</v>
+        <v>-2400</v>
       </c>
       <c r="E94" s="3">
         <v>200</v>
@@ -3872,10 +3872,10 @@
         <v>2600</v>
       </c>
       <c r="H94" s="3">
-        <v>-2700</v>
+        <v>-2800</v>
       </c>
       <c r="I94" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
@@ -4082,13 +4082,13 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>10600</v>
+        <v>10800</v>
       </c>
       <c r="E100" s="3">
-        <v>-17100</v>
+        <v>-17400</v>
       </c>
       <c r="F100" s="3">
-        <v>-2700</v>
+        <v>-2800</v>
       </c>
       <c r="G100" s="3">
         <v>-300</v>
@@ -4167,19 +4167,19 @@
         <v>2700</v>
       </c>
       <c r="E102" s="3">
-        <v>-22000</v>
+        <v>-22400</v>
       </c>
       <c r="F102" s="3">
-        <v>-2900</v>
+        <v>-3000</v>
       </c>
       <c r="G102" s="3">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="H102" s="3">
-        <v>-4200</v>
+        <v>-4300</v>
       </c>
       <c r="I102" s="3">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="J102" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/MLGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MLGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
   <si>
     <t>MLGO</t>
   </si>
@@ -656,145 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
-        <v>44834</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>81800</v>
+        <v>20000</v>
       </c>
       <c r="E8" s="3">
-        <v>37200</v>
+        <v>20100</v>
       </c>
       <c r="F8" s="3">
-        <v>2500</v>
+        <v>22300</v>
       </c>
       <c r="G8" s="3">
-        <v>82600</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>4</v>
+        <v>21700</v>
+      </c>
+      <c r="H8" s="3">
+        <v>18500</v>
       </c>
       <c r="I8" s="3">
+        <v>17800</v>
+      </c>
+      <c r="J8" s="3">
+        <v>18100</v>
+      </c>
+      <c r="K8" s="3">
         <v>48800</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>57200</v>
+        <v>14000</v>
       </c>
       <c r="E9" s="3">
-        <v>25800</v>
+        <v>14100</v>
       </c>
       <c r="F9" s="3">
-        <v>1800</v>
+        <v>15700</v>
       </c>
       <c r="G9" s="3">
-        <v>64700</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
+        <v>15300</v>
+      </c>
+      <c r="H9" s="3">
+        <v>12400</v>
       </c>
       <c r="I9" s="3">
+        <v>12900</v>
+      </c>
+      <c r="J9" s="3">
+        <v>14700</v>
+      </c>
+      <c r="K9" s="3">
         <v>39000</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
@@ -807,35 +821,41 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>24500</v>
+        <v>6000</v>
       </c>
       <c r="E10" s="3">
-        <v>11300</v>
+        <v>6100</v>
       </c>
       <c r="F10" s="3">
-        <v>700</v>
+        <v>6600</v>
       </c>
       <c r="G10" s="3">
-        <v>18000</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
+        <v>6400</v>
+      </c>
+      <c r="H10" s="3">
+        <v>6200</v>
       </c>
       <c r="I10" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K10" s="3">
         <v>9800</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
@@ -848,8 +868,14 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,35 +891,37 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>22700</v>
+        <v>5200</v>
       </c>
       <c r="E12" s="3">
-        <v>13000</v>
+        <v>5300</v>
       </c>
       <c r="F12" s="3">
-        <v>700</v>
+        <v>4900</v>
       </c>
       <c r="G12" s="3">
-        <v>13200</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>4</v>
+        <v>4700</v>
+      </c>
+      <c r="H12" s="3">
+        <v>7500</v>
       </c>
       <c r="I12" s="3">
+        <v>5200</v>
+      </c>
+      <c r="J12" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K12" s="3">
         <v>5700</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
@@ -906,8 +934,14 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,49 +981,61 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>15900</v>
+        <v>-100</v>
       </c>
       <c r="E14" s="3">
-        <v>3200</v>
+        <v>-100</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="G14" s="3">
-        <v>7200</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
+        <v>8100</v>
+      </c>
+      <c r="H14" s="3">
+        <v>3300</v>
       </c>
       <c r="I14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J14" s="3">
+        <v>7100</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1000,19 +1046,19 @@
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1029,8 +1075,14 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,90 +1095,104 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>116300</v>
+        <v>19800</v>
       </c>
       <c r="E17" s="3">
-        <v>43300</v>
+        <v>19900</v>
       </c>
       <c r="F17" s="3">
-        <v>2700</v>
+        <v>30200</v>
       </c>
       <c r="G17" s="3">
-        <v>90100</v>
+        <v>29300</v>
       </c>
       <c r="H17" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="I17" s="3">
+        <v>19200</v>
+      </c>
+      <c r="J17" s="3">
+        <v>20700</v>
+      </c>
+      <c r="K17" s="3">
         <v>46700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>200</v>
       </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
         <v>300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-34600</v>
+        <v>200</v>
       </c>
       <c r="E18" s="3">
-        <v>-6200</v>
+        <v>200</v>
       </c>
       <c r="F18" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L18" s="3">
         <v>-200</v>
       </c>
-      <c r="G18" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3">
         <v>-200</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,72 +1208,80 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-3300</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>400</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="3">
-        <v>200</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-37700</v>
+        <v>200</v>
       </c>
       <c r="E21" s="3">
-        <v>-5900</v>
+        <v>200</v>
       </c>
       <c r="F21" s="3">
-        <v>-200</v>
+        <v>-7800</v>
       </c>
       <c r="G21" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+        <v>-7600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-2100</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -1224,8 +1298,14 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1265,90 +1345,108 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-37900</v>
+        <v>1600</v>
       </c>
       <c r="E23" s="3">
-        <v>-5900</v>
+        <v>1600</v>
       </c>
       <c r="F23" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="K23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L23" s="3">
         <v>-200</v>
       </c>
-      <c r="G23" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="H23" s="3">
-        <v>100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O23" s="3">
         <v>-200</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>4</v>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,90 +1486,108 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-37500</v>
+        <v>1500</v>
       </c>
       <c r="E26" s="3">
-        <v>-5900</v>
+        <v>1500</v>
       </c>
       <c r="F26" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="K26" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="H26" s="3">
-        <v>100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-37800</v>
+        <v>1100</v>
       </c>
       <c r="E27" s="3">
-        <v>-5200</v>
+        <v>1100</v>
       </c>
       <c r="F27" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="K27" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L27" s="3">
         <v>-200</v>
       </c>
-      <c r="G27" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="H27" s="3">
-        <v>100</v>
-      </c>
-      <c r="I27" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O27" s="3">
         <v>-200</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1627,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1552,8 +1674,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1721,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,90 +1768,108 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-37800</v>
+        <v>1100</v>
       </c>
       <c r="E33" s="3">
-        <v>-5200</v>
+        <v>1100</v>
       </c>
       <c r="F33" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="K33" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="G33" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="H33" s="3">
-        <v>100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,95 +1909,113 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-37800</v>
+        <v>1100</v>
       </c>
       <c r="E35" s="3">
-        <v>-5200</v>
+        <v>1100</v>
       </c>
       <c r="F35" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="K35" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="G35" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="H35" s="3">
-        <v>100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
-        <v>44834</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +2031,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,31 +2050,33 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>60000</v>
+      </c>
+      <c r="F41" s="3">
         <v>44700</v>
       </c>
-      <c r="E41" s="3">
-        <v>19600</v>
-      </c>
-      <c r="F41" s="3">
-        <v>3000</v>
-      </c>
       <c r="G41" s="3">
-        <v>42000</v>
+        <v>43500</v>
       </c>
       <c r="H41" s="3">
-        <v>0</v>
+        <v>19100</v>
       </c>
       <c r="I41" s="3">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>43200</v>
       </c>
       <c r="K41" s="3">
         <v>0</v>
@@ -1914,42 +2088,48 @@
         <v>0</v>
       </c>
       <c r="N41" s="3">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3">
         <v>200</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F42" s="3">
         <v>2600</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="G42" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -1960,31 +2140,37 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>32400</v>
+      </c>
+      <c r="F43" s="3">
         <v>3400</v>
       </c>
-      <c r="E43" s="3">
-        <v>30800</v>
-      </c>
-      <c r="F43" s="3">
-        <v>200</v>
-      </c>
       <c r="G43" s="3">
-        <v>8500</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
+        <v>3300</v>
+      </c>
+      <c r="H43" s="3">
+        <v>30100</v>
+      </c>
+      <c r="I43" s="3">
+        <v>27500</v>
+      </c>
+      <c r="J43" s="3">
+        <v>2900</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
@@ -1992,81 +2178,93 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>100</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>6800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>6600</v>
-      </c>
-      <c r="F45" s="3">
-        <v>5100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>4500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2075,39 +2273,45 @@
         <v>0</v>
       </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>105300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>105900</v>
+      </c>
+      <c r="F46" s="3">
         <v>57600</v>
       </c>
-      <c r="E46" s="3">
-        <v>56900</v>
-      </c>
-      <c r="F46" s="3">
-        <v>8300</v>
-      </c>
       <c r="G46" s="3">
-        <v>54200</v>
+        <v>56000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>55700</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>58700</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>55800</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2116,16 +2320,22 @@
         <v>0</v>
       </c>
       <c r="M46" s="3">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3">
+        <v>0</v>
+      </c>
+      <c r="O46" s="3">
         <v>100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>300</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2133,40 +2343,46 @@
         <v>0</v>
       </c>
       <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
         <v>200</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>200</v>
       </c>
-      <c r="H47" s="3">
-        <v>6800</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
+        <v>200</v>
+      </c>
+      <c r="K47" s="3">
         <v>6700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>6600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>6500</v>
-      </c>
-      <c r="L47" s="3">
-        <v>46500</v>
-      </c>
-      <c r="M47" s="3">
-        <v>46500</v>
       </c>
       <c r="N47" s="3">
         <v>46500</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>46500</v>
+      </c>
+      <c r="P47" s="3">
+        <v>46500</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2177,19 +2393,19 @@
         <v>200</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G48" s="3">
+        <v>200</v>
+      </c>
+      <c r="H48" s="3">
+        <v>200</v>
+      </c>
+      <c r="I48" s="3">
         <v>300</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
+      <c r="J48" s="3">
+        <v>300</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
@@ -2197,17 +2413,23 @@
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2215,22 +2437,22 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>15900</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>15900</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>15500</v>
+      </c>
+      <c r="I49" s="3">
+        <v>16400</v>
+      </c>
+      <c r="J49" s="3">
+        <v>16400</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>4</v>
@@ -2238,17 +2460,23 @@
       <c r="L49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2516,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,13 +2563,19 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -2344,17 +2584,17 @@
         <v>0</v>
       </c>
       <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
@@ -2368,10 +2608,16 @@
         <v>0</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,49 +2657,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>105500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>106200</v>
+      </c>
+      <c r="F54" s="3">
         <v>57900</v>
       </c>
-      <c r="E54" s="3">
-        <v>73200</v>
-      </c>
-      <c r="F54" s="3">
-        <v>10700</v>
-      </c>
       <c r="G54" s="3">
-        <v>70800</v>
+        <v>56300</v>
       </c>
       <c r="H54" s="3">
-        <v>6800</v>
+        <v>71600</v>
       </c>
       <c r="I54" s="3">
+        <v>75600</v>
+      </c>
+      <c r="J54" s="3">
+        <v>72800</v>
+      </c>
+      <c r="K54" s="3">
         <v>6700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>6600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>6500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>46500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>46600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>46800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2727,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,31 +2746,33 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F57" s="3">
         <v>3000</v>
       </c>
-      <c r="E57" s="3">
-        <v>5000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>300</v>
-      </c>
       <c r="G57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
+        <v>2900</v>
+      </c>
+      <c r="H57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J57" s="3">
+        <v>2100</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
@@ -2518,148 +2780,172 @@
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>22800</v>
+      </c>
+      <c r="F58" s="3">
         <v>1900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H58" s="3">
         <v>1200</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H58" s="3">
-        <v>300</v>
       </c>
       <c r="I58" s="3">
         <v>200</v>
       </c>
       <c r="J58" s="3">
+        <v>200</v>
+      </c>
+      <c r="K58" s="3">
+        <v>200</v>
+      </c>
+      <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>200</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7200</v>
+        <v>5000</v>
       </c>
       <c r="E59" s="3">
-        <v>5600</v>
+        <v>5000</v>
       </c>
       <c r="F59" s="3">
-        <v>800</v>
+        <v>7100</v>
       </c>
       <c r="G59" s="3">
-        <v>2700</v>
+        <v>6900</v>
       </c>
       <c r="H59" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="I59" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
       </c>
       <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
-      </c>
-      <c r="N59" s="3">
-        <v>0</v>
-      </c>
       <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>29800</v>
+      </c>
+      <c r="F60" s="3">
         <v>12000</v>
       </c>
-      <c r="E60" s="3">
-        <v>11800</v>
-      </c>
-      <c r="F60" s="3">
-        <v>1200</v>
-      </c>
       <c r="G60" s="3">
-        <v>4700</v>
+        <v>11700</v>
       </c>
       <c r="H60" s="3">
+        <v>11600</v>
+      </c>
+      <c r="I60" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J60" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K60" s="3">
+        <v>200</v>
+      </c>
+      <c r="L60" s="3">
+        <v>100</v>
+      </c>
+      <c r="M60" s="3">
+        <v>100</v>
+      </c>
+      <c r="N60" s="3">
         <v>300</v>
       </c>
-      <c r="I60" s="3">
-        <v>200</v>
-      </c>
-      <c r="J60" s="3">
-        <v>100</v>
-      </c>
-      <c r="K60" s="3">
-        <v>100</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3">
         <v>300</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
-      <c r="O60" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2671,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2691,49 +2977,61 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>300</v>
-      </c>
-      <c r="H62" s="3">
-        <v>200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>200</v>
-      </c>
-      <c r="J62" s="3">
-        <v>200</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K62" s="3">
         <v>200</v>
       </c>
       <c r="L62" s="3">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="M62" s="3">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="N62" s="3">
         <v>1500</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +3071,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +3118,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,49 +3165,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>12600</v>
+        <v>29700</v>
       </c>
       <c r="E66" s="3">
-        <v>11600</v>
+        <v>29900</v>
       </c>
       <c r="F66" s="3">
-        <v>1300</v>
+        <v>12000</v>
       </c>
       <c r="G66" s="3">
-        <v>5200</v>
+        <v>11700</v>
       </c>
       <c r="H66" s="3">
-        <v>500</v>
+        <v>11800</v>
       </c>
       <c r="I66" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="K66" s="3">
         <v>400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3235,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3278,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3325,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,8 +3372,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,49 +3419,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-9000</v>
       </c>
-      <c r="E72" s="3">
-        <v>15300</v>
-      </c>
-      <c r="F72" s="3">
-        <v>2800</v>
-      </c>
       <c r="G72" s="3">
-        <v>20000</v>
+        <v>-8800</v>
       </c>
       <c r="H72" s="3">
-        <v>-500</v>
+        <v>15000</v>
       </c>
       <c r="I72" s="3">
+        <v>19700</v>
+      </c>
+      <c r="J72" s="3">
+        <v>20500</v>
+      </c>
+      <c r="K72" s="3">
         <v>-400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-1200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3513,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3560,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,49 +3607,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>75000</v>
+      </c>
+      <c r="F76" s="3">
         <v>45300</v>
       </c>
-      <c r="E76" s="3">
-        <v>61500</v>
-      </c>
-      <c r="F76" s="3">
-        <v>9400</v>
-      </c>
       <c r="G76" s="3">
-        <v>65500</v>
+        <v>44000</v>
       </c>
       <c r="H76" s="3">
-        <v>6300</v>
+        <v>60200</v>
       </c>
       <c r="I76" s="3">
-        <v>6200</v>
+        <v>66700</v>
       </c>
       <c r="J76" s="3">
-        <v>6200</v>
+        <v>67400</v>
       </c>
       <c r="K76" s="3">
         <v>6200</v>
       </c>
       <c r="L76" s="3">
+        <v>6200</v>
+      </c>
+      <c r="M76" s="3">
+        <v>6200</v>
+      </c>
+      <c r="N76" s="3">
         <v>44700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>45000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>45200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,95 +3701,113 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
-        <v>44834</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-37800</v>
+        <v>1100</v>
       </c>
       <c r="E81" s="3">
-        <v>-5200</v>
+        <v>1100</v>
       </c>
       <c r="F81" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="K81" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="G81" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="H81" s="3">
-        <v>100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,31 +3823,33 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G83" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>200</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>4</v>
@@ -3459,17 +3857,23 @@
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +3913,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +3960,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +4007,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +4054,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,49 +4101,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-6400</v>
+        <v>-300</v>
       </c>
       <c r="E89" s="3">
-        <v>-6400</v>
+        <v>-400</v>
       </c>
       <c r="F89" s="3">
         <v>0</v>
       </c>
       <c r="G89" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>-400</v>
+        <v>-3500</v>
       </c>
       <c r="I89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="J89" s="3">
+        <v>900</v>
+      </c>
+      <c r="K89" s="3">
         <v>300</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
       <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,29 +4171,31 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3">
+        <v>100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -3772,8 +4214,14 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4261,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,35 +4308,41 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2400</v>
+        <v>-600</v>
       </c>
       <c r="E94" s="3">
-        <v>200</v>
+        <v>-600</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="G94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="H94" s="3">
+        <v>500</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>2600</v>
       </c>
-      <c r="H94" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="I94" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
@@ -3890,13 +4350,19 @@
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-46500</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,31 +4378,33 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3953,8 +4421,14 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4468,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4515,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,72 +4562,84 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>10800</v>
+        <v>8800</v>
       </c>
       <c r="E100" s="3">
-        <v>-17400</v>
+        <v>8800</v>
       </c>
       <c r="F100" s="3">
-        <v>-2800</v>
+        <v>14100</v>
       </c>
       <c r="G100" s="3">
-        <v>-300</v>
+        <v>13700</v>
       </c>
       <c r="H100" s="3">
-        <v>-300</v>
+        <v>2600</v>
       </c>
       <c r="I100" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="J100" s="3">
+        <v>19000</v>
+      </c>
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>46900</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3">
         <v>1200</v>
       </c>
       <c r="F101" s="3">
-        <v>-200</v>
+        <v>1900</v>
       </c>
       <c r="G101" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>4</v>
+        <v>-1200</v>
+      </c>
+      <c r="H101" s="3">
+        <v>900</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>700</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>4</v>
@@ -4149,54 +4647,66 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>2700</v>
+        <v>8000</v>
       </c>
       <c r="E102" s="3">
-        <v>-22400</v>
+        <v>8000</v>
       </c>
       <c r="F102" s="3">
-        <v>-3000</v>
+        <v>12600</v>
       </c>
       <c r="G102" s="3">
-        <v>3600</v>
+        <v>12200</v>
       </c>
       <c r="H102" s="3">
-        <v>-4300</v>
+        <v>-500</v>
       </c>
       <c r="I102" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="J102" s="3">
+        <v>21900</v>
+      </c>
+      <c r="K102" s="3">
         <v>4300</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MLGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MLGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
   <si>
     <t>MLGO</t>
   </si>
@@ -656,165 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>17900</v>
+      </c>
+      <c r="F8" s="3">
         <v>20000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>20100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>22300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>21700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>18500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>17800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>18100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>48800</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>13200</v>
+      </c>
+      <c r="F9" s="3">
         <v>14000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>14100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>15700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>15300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>12400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>12900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>14700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>39000</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
@@ -827,41 +840,47 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F10" s="3">
         <v>6000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>6100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>6600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>6400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>6200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>5000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>3400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>9800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
@@ -874,8 +893,14 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -893,41 +918,43 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F12" s="3">
         <v>5200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>5300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>4900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>4700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>7500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>5200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>3700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>5700</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
@@ -940,8 +967,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -987,55 +1020,67 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>100</v>
+      </c>
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>8300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>8100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>3300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>7100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1046,26 +1091,26 @@
         <v>0</v>
       </c>
       <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
         <v>100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>100</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
       </c>
       <c r="I15" s="3">
         <v>100</v>
       </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
+        <v>100</v>
+      </c>
+      <c r="L15" s="3">
         <v>300</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1081,8 +1126,14 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,102 +1148,116 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F17" s="3">
         <v>19800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>19900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>30200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>29300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>20000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>19200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>20700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>46700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
         <v>300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F18" s="3">
         <v>200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-7900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-7700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-200</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1210,8 +1275,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1234,61 +1301,67 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F21" s="3">
         <v>200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-7800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-7600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1304,8 +1377,14 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1351,102 +1430,120 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F23" s="3">
         <v>1600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-16000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-15500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-4500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-9500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-200</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
         <v>-300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>400</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>4</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1492,102 +1589,120 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F26" s="3">
         <v>1500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-15800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-15400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-4500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-9100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-200</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>-300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F27" s="3">
         <v>1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-16300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-15800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-9100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-200</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
         <v>-300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1633,8 +1748,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1680,8 +1801,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1727,8 +1854,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1774,8 +1907,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1798,78 +1937,90 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F33" s="3">
         <v>1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-16300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-15800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-9100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-200</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>-300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1915,107 +2066,125 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F35" s="3">
         <v>1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-16300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-15800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-9100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-200</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>-300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2033,8 +2202,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2052,38 +2223,40 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>141900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>147700</v>
+      </c>
+      <c r="F41" s="3">
         <v>59600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>60000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>44700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>43500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>19100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>21000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>43200</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
       <c r="M41" s="3">
         <v>0</v>
       </c>
@@ -2094,48 +2267,54 @@
         <v>0</v>
       </c>
       <c r="P41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+      <c r="R41" s="3">
         <v>200</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F42" s="3">
         <v>5700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>5800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>2600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>2500</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2146,55 +2325,67 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F43" s="3">
         <v>32200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>32400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>3400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>30100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>27500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2900</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2216,32 +2407,38 @@
       <c r="I44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>100</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2263,15 +2460,15 @@
       <c r="I45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>5800</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2279,46 +2476,52 @@
         <v>0</v>
       </c>
       <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>100</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>173200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>180300</v>
+      </c>
+      <c r="F46" s="3">
         <v>105300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>105900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>57600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>56000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>55700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>58700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>55800</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2326,16 +2529,22 @@
         <v>0</v>
       </c>
       <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3">
         <v>100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>300</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2352,45 +2561,51 @@
         <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3">
         <v>200</v>
       </c>
       <c r="K47" s="3">
+        <v>200</v>
+      </c>
+      <c r="L47" s="3">
+        <v>200</v>
+      </c>
+      <c r="M47" s="3">
         <v>6700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>6600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>6500</v>
-      </c>
-      <c r="N47" s="3">
-        <v>46500</v>
-      </c>
-      <c r="O47" s="3">
-        <v>46500</v>
       </c>
       <c r="P47" s="3">
         <v>46500</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>46500</v>
+      </c>
+      <c r="R47" s="3">
+        <v>46500</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F48" s="3">
         <v>200</v>
@@ -2402,34 +2617,40 @@
         <v>200</v>
       </c>
       <c r="I48" s="3">
+        <v>200</v>
+      </c>
+      <c r="J48" s="3">
+        <v>200</v>
+      </c>
+      <c r="K48" s="3">
         <v>300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>300</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2446,37 +2667,43 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>15500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>16400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>16400</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2522,8 +2749,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2569,8 +2802,14 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2593,14 +2832,14 @@
         <v>0</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -2614,10 +2853,16 @@
         <v>0</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2663,55 +2908,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>173600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>180600</v>
+      </c>
+      <c r="F54" s="3">
         <v>105500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>106200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>57900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>56300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>71600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>75600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>72800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>6700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>6600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>6500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>46500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>46600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>46800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2729,8 +2986,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2748,55 +3007,63 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>4900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3">
-        <v>0</v>
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2804,140 +3071,158 @@
         <v>22600</v>
       </c>
       <c r="E58" s="3">
+        <v>23500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>22600</v>
+      </c>
+      <c r="G58" s="3">
         <v>22800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1200</v>
-      </c>
-      <c r="I58" s="3">
-        <v>200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>200</v>
       </c>
       <c r="K58" s="3">
         <v>200</v>
       </c>
       <c r="L58" s="3">
+        <v>200</v>
+      </c>
+      <c r="M58" s="3">
+        <v>200</v>
+      </c>
+      <c r="N58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>200</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F59" s="3">
         <v>5000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>5000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>7100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>6900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>5300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2600</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
       <c r="M59" s="3">
         <v>0</v>
       </c>
       <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
       <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>29500</v>
+      </c>
+      <c r="F60" s="3">
         <v>29600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>29800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>12000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>11700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>11600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>8400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>300</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2948,23 +3233,23 @@
         <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2983,8 +3268,14 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3009,29 +3300,35 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
-        <v>200</v>
-      </c>
-      <c r="L62" s="3">
-        <v>200</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>200</v>
       </c>
       <c r="N62" s="3">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="O62" s="3">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="P62" s="3">
         <v>1500</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3077,8 +3374,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3124,8 +3427,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3171,55 +3480,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>29600</v>
+      </c>
+      <c r="F66" s="3">
         <v>29700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>29900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>12000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>11700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>11800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>8700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3237,8 +3558,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3284,8 +3607,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3331,8 +3660,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3378,8 +3713,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3425,55 +3766,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-6600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-6600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-9000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-8800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>15000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>19700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>20500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-1800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3519,8 +3872,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3566,8 +3925,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3613,55 +3978,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>142700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>148500</v>
+      </c>
+      <c r="F76" s="3">
         <v>74500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>75000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>45300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>44000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>60200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>66700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>67400</v>
-      </c>
-      <c r="K76" s="3">
-        <v>6200</v>
-      </c>
-      <c r="L76" s="3">
-        <v>6200</v>
       </c>
       <c r="M76" s="3">
         <v>6200</v>
       </c>
       <c r="N76" s="3">
+        <v>6200</v>
+      </c>
+      <c r="O76" s="3">
+        <v>6200</v>
+      </c>
+      <c r="P76" s="3">
         <v>44700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>45000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>45200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3707,107 +4084,125 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F81" s="3">
         <v>1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-16300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-15800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-9100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-200</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>-300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3825,55 +4220,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
       </c>
       <c r="H83" s="3">
+        <v>300</v>
+      </c>
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
+        <v>100</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3919,8 +4322,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3966,8 +4375,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4013,8 +4428,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4060,8 +4481,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4107,55 +4534,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-400</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>-3500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>300</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
       <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4173,8 +4612,10 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4184,24 +4625,24 @@
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3">
         <v>100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -4220,8 +4661,14 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4267,8 +4714,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4314,41 +4767,47 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>2600</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
@@ -4356,13 +4815,19 @@
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-46500</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4380,8 +4845,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4406,11 +4873,11 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4427,8 +4894,14 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4474,8 +4947,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4521,8 +5000,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4568,145 +5053,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>48600</v>
+      </c>
+      <c r="F100" s="3">
         <v>8800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>8800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>14100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>13700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>2600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-19600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>19000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>46900</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>900</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>700</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>42900</v>
+      </c>
+      <c r="F102" s="3">
         <v>8000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>8000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>12600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>12200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-21500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>21900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>4300</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MLGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MLGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
   <si>
     <t>MLGO</t>
   </si>
@@ -656,204 +656,217 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>16400</v>
+      </c>
+      <c r="F8" s="3">
         <v>13100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>13000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>17200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>17900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>20000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>20100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>22300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>21700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>18500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>17800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>18100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>48800</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F9" s="3">
         <v>9500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>9400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>12700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>13200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>14000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>14100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>15700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>15300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>12400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>12900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>14700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>39000</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
@@ -866,53 +879,59 @@
       <c r="U9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F10" s="3">
         <v>3600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>3600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>4500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>4700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>6000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>6100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>6600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>6400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>6200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>5000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>3400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>9800</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
@@ -925,8 +944,14 @@
       <c r="U10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -948,53 +973,55 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F12" s="3">
         <v>2300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>2300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>2500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>2600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>5200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>5300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>4900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>4700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>7500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>5200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>3700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>5700</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
@@ -1007,8 +1034,14 @@
       <c r="U12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1066,8 +1099,14 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1077,56 +1116,62 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>8300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>8100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>3300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>7100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1149,26 +1194,26 @@
         <v>0</v>
       </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>100</v>
-      </c>
-      <c r="K15" s="3">
-        <v>100</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
       </c>
       <c r="M15" s="3">
         <v>100</v>
       </c>
       <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>100</v>
+      </c>
+      <c r="P15" s="3">
         <v>300</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1184,8 +1229,14 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1204,126 +1255,140 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F17" s="3">
         <v>12600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>12400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>16000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>16700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>19800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>19900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>30200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>29300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>20000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>19200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>20700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>46700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>200</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3">
         <v>300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F18" s="3">
         <v>600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-7900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-7700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>2000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U18" s="3">
         <v>-200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1345,8 +1410,10 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1381,73 +1448,79 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F21" s="3">
         <v>600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>1300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-7800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-7600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-2100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1463,16 +1536,22 @@
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1522,126 +1601,144 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2400</v>
+        <v>7200</v>
       </c>
       <c r="E23" s="3">
-        <v>2300</v>
+        <v>7100</v>
       </c>
       <c r="F23" s="3">
         <v>2400</v>
       </c>
       <c r="G23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H23" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I23" s="3">
         <v>2500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-16000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-15500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-4500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-9500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>2200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
         <v>-300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>400</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>4</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1699,126 +1796,144 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F26" s="3">
         <v>2200</v>
-      </c>
-      <c r="E26" s="3">
-        <v>2200</v>
-      </c>
-      <c r="F26" s="3">
-        <v>2100</v>
       </c>
       <c r="G26" s="3">
         <v>2200</v>
       </c>
       <c r="H26" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I26" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J26" s="3">
         <v>1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-15800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-15400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-9100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
         <v>-300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F27" s="3">
         <v>1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-16300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-15800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-3900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-9100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
         <v>-300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1876,8 +1991,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1935,8 +2056,14 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1994,8 +2121,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2053,8 +2186,14 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2089,90 +2228,102 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F33" s="3">
         <v>1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-16300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-15800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-9100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>-300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2230,131 +2381,149 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F35" s="3">
         <v>1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-16300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-15800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-9100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>2300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>-300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2376,8 +2545,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2399,50 +2570,52 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>175700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>172600</v>
+      </c>
+      <c r="F41" s="3">
         <v>253100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>249900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>141900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>147700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>59600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>60000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>44700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>43500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>19100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>21000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>43200</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
       <c r="Q41" s="3">
         <v>0</v>
       </c>
@@ -2453,60 +2626,66 @@
         <v>0</v>
       </c>
       <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
+        <v>0</v>
+      </c>
+      <c r="V41" s="3">
         <v>200</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="W41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>162700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>159900</v>
+      </c>
+      <c r="F42" s="3">
         <v>66000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>65200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>20500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>21300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>5700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>5800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>2600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>2500</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2517,67 +2696,79 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3600</v>
+        <v>6500</v>
       </c>
       <c r="E43" s="3">
-        <v>3500</v>
+        <v>6400</v>
       </c>
       <c r="F43" s="3">
         <v>3600</v>
       </c>
       <c r="G43" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I43" s="3">
         <v>3700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>32200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>32400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>30100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>27500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2900</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2611,32 +2802,38 @@
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>100</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
-      </c>
-      <c r="T44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2670,15 +2867,15 @@
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>5800</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -2686,58 +2883,64 @@
         <v>0</v>
       </c>
       <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>351900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>345700</v>
+      </c>
+      <c r="F46" s="3">
         <v>330300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>326100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>173200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>180300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>105300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>105900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>57600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>56000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>55700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>58700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>55800</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -2745,16 +2948,22 @@
         <v>0</v>
       </c>
       <c r="S46" s="3">
+        <v>0</v>
+      </c>
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+      <c r="U46" s="3">
         <v>100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>300</v>
       </c>
-      <c r="U46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2783,57 +2992,63 @@
         <v>0</v>
       </c>
       <c r="L47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N47" s="3">
         <v>200</v>
       </c>
       <c r="O47" s="3">
+        <v>200</v>
+      </c>
+      <c r="P47" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q47" s="3">
         <v>6700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>6600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>6500</v>
-      </c>
-      <c r="R47" s="3">
-        <v>46500</v>
-      </c>
-      <c r="S47" s="3">
-        <v>46500</v>
       </c>
       <c r="T47" s="3">
         <v>46500</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>46500</v>
+      </c>
+      <c r="V47" s="3">
+        <v>46500</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>100</v>
+      </c>
+      <c r="F48" s="3">
         <v>200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>200</v>
-      </c>
-      <c r="I48" s="3">
-        <v>200</v>
       </c>
       <c r="J48" s="3">
         <v>200</v>
@@ -2845,34 +3060,40 @@
         <v>200</v>
       </c>
       <c r="M48" s="3">
+        <v>200</v>
+      </c>
+      <c r="N48" s="3">
+        <v>200</v>
+      </c>
+      <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>300</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2901,37 +3122,43 @@
         <v>0</v>
       </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>15500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>16400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>16400</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
-      </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2989,8 +3216,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3048,16 +3281,22 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
@@ -3084,14 +3323,14 @@
         <v>0</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
@@ -3105,10 +3344,16 @@
         <v>0</v>
       </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3166,67 +3411,79 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>352100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>345900</v>
+      </c>
+      <c r="F54" s="3">
         <v>330600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>326400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>173600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>180600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>105500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>106200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>57900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>56300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>71600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>75600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>72800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>6700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>6600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>6500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>46500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>46600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>46800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3248,8 +3505,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3271,252 +3530,278 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F57" s="3">
         <v>2300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>4900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2100</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
-      <c r="T57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E58" s="3">
         <v>4300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G58" s="3">
         <v>4200</v>
-      </c>
-      <c r="F58" s="3">
-        <v>22600</v>
-      </c>
-      <c r="G58" s="3">
-        <v>23500</v>
       </c>
       <c r="H58" s="3">
         <v>22600</v>
       </c>
       <c r="I58" s="3">
+        <v>23500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>22600</v>
+      </c>
+      <c r="K58" s="3">
         <v>22800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1200</v>
-      </c>
-      <c r="M58" s="3">
-        <v>200</v>
-      </c>
-      <c r="N58" s="3">
-        <v>200</v>
       </c>
       <c r="O58" s="3">
         <v>200</v>
       </c>
       <c r="P58" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>200</v>
+      </c>
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>200</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F59" s="3">
         <v>3400</v>
-      </c>
-      <c r="E59" s="3">
-        <v>3300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>3100</v>
       </c>
       <c r="G59" s="3">
         <v>3300</v>
       </c>
       <c r="H59" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I59" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J59" s="3">
         <v>5000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>7100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>6900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>5300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>5900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2600</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
       <c r="Q59" s="3">
         <v>0</v>
       </c>
       <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
-      <c r="T59" s="3">
-        <v>0</v>
-      </c>
       <c r="U59" s="3">
+        <v>0</v>
+      </c>
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F60" s="3">
         <v>10000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>9900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>28300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>29500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>29600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>29800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>12000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>11700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>11600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>8400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>4900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>300</v>
       </c>
-      <c r="S60" s="3">
-        <v>0</v>
-      </c>
-      <c r="T60" s="3">
-        <v>0</v>
-      </c>
       <c r="U60" s="3">
+        <v>0</v>
+      </c>
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+      <c r="W60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>100</v>
@@ -3531,23 +3816,23 @@
         <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>100</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3566,8 +3851,14 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3604,29 +3895,35 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
-        <v>200</v>
-      </c>
-      <c r="P62" s="3">
-        <v>200</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q62" s="3">
         <v>200</v>
       </c>
       <c r="R62" s="3">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="S62" s="3">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="T62" s="3">
         <v>1500</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="V62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3684,8 +3981,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3743,8 +4046,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3802,67 +4111,79 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F66" s="3">
         <v>10000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>9900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>28400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>29600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>29700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>29900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>12000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>11700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>11800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>8700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>5100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3884,8 +4205,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3943,8 +4266,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4002,8 +4331,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4061,8 +4396,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4120,67 +4461,79 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F72" s="3">
         <v>100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-3500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-3600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-6600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-6600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-9000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-8800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>15000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>19700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>20500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-1800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-1200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4238,8 +4591,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4297,8 +4656,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4356,67 +4721,79 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>332000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>326100</v>
+      </c>
+      <c r="F76" s="3">
         <v>317300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>313300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>142700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>148500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>74500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>75000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>45300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>44000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>60200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>66700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>67400</v>
-      </c>
-      <c r="O76" s="3">
-        <v>6200</v>
-      </c>
-      <c r="P76" s="3">
-        <v>6200</v>
       </c>
       <c r="Q76" s="3">
         <v>6200</v>
       </c>
       <c r="R76" s="3">
+        <v>6200</v>
+      </c>
+      <c r="S76" s="3">
+        <v>6200</v>
+      </c>
+      <c r="T76" s="3">
         <v>44700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>45000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>45200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4474,131 +4851,149 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F81" s="3">
         <v>1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-16300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-15800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-9100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>2300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>-300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4620,8 +5015,10 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4632,55 +5029,61 @@
         <v>0</v>
       </c>
       <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
       </c>
       <c r="L83" s="3">
+        <v>300</v>
+      </c>
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
+        <v>100</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4738,8 +5141,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4797,8 +5206,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4856,8 +5271,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4915,8 +5336,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4974,67 +5401,79 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F89" s="3">
         <v>2200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>2100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>2400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>2400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
       <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
         <v>-3500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>300</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5056,22 +5495,24 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -5079,24 +5520,24 @@
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N91" s="3">
         <v>100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -5115,8 +5556,14 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5174,8 +5621,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5233,53 +5686,59 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-22700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-22400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-8000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-8300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>2600</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -5287,13 +5746,19 @@
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-46500</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5315,8 +5780,10 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5353,11 +5820,11 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5374,8 +5841,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5433,8 +5906,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5492,8 +5971,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5551,181 +6036,205 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>200</v>
+      </c>
+      <c r="F100" s="3">
         <v>75300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>74400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>46700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>48600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>8800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>8800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>14100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>13700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>2600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-19600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>19000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>46900</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>200</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>1200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>1900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-1200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>900</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>700</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="F102" s="3">
         <v>54300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>53600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>41300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>42900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>8000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>8000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>12600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>12200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-21500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>21900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>4300</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
         <v>0</v>
       </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>0</v>
       </c>
     </row>
